--- a/artfynd/A 2938-2021 artfynd.xlsx
+++ b/artfynd/A 2938-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127153980</v>
       </c>
       <c r="B2" t="n">
-        <v>101376</v>
+        <v>101451</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2938-2021 artfynd.xlsx
+++ b/artfynd/A 2938-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127153980</v>
       </c>
       <c r="B2" t="n">
-        <v>101451</v>
+        <v>101457</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2938-2021 artfynd.xlsx
+++ b/artfynd/A 2938-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127153980</v>
       </c>
       <c r="B2" t="n">
-        <v>101457</v>
+        <v>101458</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2938-2021 artfynd.xlsx
+++ b/artfynd/A 2938-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127153980</v>
       </c>
       <c r="B2" t="n">
-        <v>101458</v>
+        <v>101462</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2938-2021 artfynd.xlsx
+++ b/artfynd/A 2938-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127153980</v>
       </c>
       <c r="B2" t="n">
-        <v>101462</v>
+        <v>101463</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2938-2021 artfynd.xlsx
+++ b/artfynd/A 2938-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127153980</v>
       </c>
       <c r="B2" t="n">
-        <v>101463</v>
+        <v>101465</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2938-2021 artfynd.xlsx
+++ b/artfynd/A 2938-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127153980</v>
       </c>
       <c r="B2" t="n">
-        <v>101465</v>
+        <v>101471</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2938-2021 artfynd.xlsx
+++ b/artfynd/A 2938-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127153980</v>
       </c>
       <c r="B2" t="n">
-        <v>101471</v>
+        <v>101474</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2938-2021 artfynd.xlsx
+++ b/artfynd/A 2938-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127153980</v>
       </c>
       <c r="B2" t="n">
-        <v>101474</v>
+        <v>101482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2938-2021 artfynd.xlsx
+++ b/artfynd/A 2938-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127153980</v>
       </c>
       <c r="B2" t="n">
-        <v>101482</v>
+        <v>101483</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2938-2021 artfynd.xlsx
+++ b/artfynd/A 2938-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127153980</v>
       </c>
       <c r="B2" t="n">
-        <v>101483</v>
+        <v>101451</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2938-2021 artfynd.xlsx
+++ b/artfynd/A 2938-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127153980</v>
       </c>
       <c r="B2" t="n">
-        <v>101451</v>
+        <v>101483</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
